--- a/output/13_대성단가_검토요약.xlsx
+++ b/output/13_대성단가_검토요약.xlsx
@@ -680,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>13457781</v>
+        <v>26915562</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>10</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>13457781</v>
+        <v>26915562</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>11455169</v>
+        <v>45820676</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>11455169</v>
+        <v>45820676</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         <v>6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>9544236</v>
+        <v>19088472</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>2182322</v>
+        <v>4364644</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -858,13 +858,13 @@
         <v>6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>9544236</v>
+        <v>19088472</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>2182322</v>
+        <v>4364644</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>8869933</v>
+        <v>35479732</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>8869933</v>
+        <v>35479732</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>

--- a/output/13_대성단가_검토요약.xlsx
+++ b/output/13_대성단가_검토요약.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요약_판단'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성별_비교상세'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'6+0_8+0_근거없음'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'직접대응_품목'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'직접대응_품목'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +115,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,7 +524,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>'대성 가격이 애니콤보다 몇 배 비싸다/싸다' 식의 직접 비교는 지금 자료로 할 수 없다 - Aviat 참고치는 발주이력에서 반복 확인된 핵심 품목 몇 개일 뿐 완성 링크가 아니고, 대성 금액은 케이블·커넥터·전원까지 포함한 완성 링크 총액이라 범위 자체가 다르다. 아래 '직접대응 품목' 3건(SFP류, 코드 매칭 없이도 비교 가능)만 유일하게 신뢰할 수 있는 가격 비교점이다.</t>
+          <t>'대성 가격이 애니콤보다 몇 배 비싸다/싸다' 식의 직접 비교는 지금 자료로 할 수 없다 - Aviat 참고치는 발주이력에서 반복 확인된 핵심 품목 몇 개일 뿐 완성 링크가 아니고, 대성 금액은 케이블·커넥터·전원까지 포함한 완성 링크 총액이라 범위 자체가 다르다. 아래 '직접대응 품목' 3건(SFP류, 코드 매칭 없이도 비교 가능)이 그나마 신뢰할 수 있는 가격 비교점이나, 3건도 스펙 일치도가 서로 달라 등급을 나눠서 봐야 한다(신뢰도 등급 열 참조).</t>
         </is>
       </c>
     </row>
@@ -533,7 +536,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SFP류 3건 모두 대성(Ceragon) 단가가 Aviat 판매가보다 낮게 나타남(상세는 직접대응_품목 시트). 다만 정식 견적 비교가 아니라 가격표상 단가 비교이며, 온도·거리 등 세부 사양 완전 일치는 아직 미확인이다.</t>
+          <t>SFP류 3건 모두 대성(Ceragon) 단가가 Aviat 판매가보다 낮게 나타나지만 신뢰도는 다르다: 실내용 1G SFP(준직접 비교, 설명 실질적 동일)가 가장 근접하고, 옥외용 1G SFP(조건부 비교, 온도등급 -40~+85℃ vs -30~+50℃로 다름)와 10G SFP+(참고 비교, 등급·거리 사양 모두 불일치 가능)는 그보다 약하다. 정식 견적 비교가 아니라 가격표상 단가 비교라는 한계도 여전하다(상세는 직접대응_품목 시트).</t>
         </is>
       </c>
     </row>
@@ -1189,13 +1192,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1206,15 +1210,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>신뢰도 등급</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Aviat 판매가</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>대성(Ceragon) 단가</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1226,15 +1235,20 @@
           <t>옥외(Outdoor)용 산업용 1G GbE SFP 광모듈</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>조건부 비교</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>130000</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="D2" s="4" t="n">
         <v>104257.351</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>양측 모두 '옥외 Outdoor용 Optic Gbit Module' 설명이 동일. 온도사양은 Aviat -40~+85℃, Ceragon -30~+50℃로 약간 다름(확인 필요).</t>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>양측 모두 '옥외 Outdoor용 Optic Gbit Module' 설명이 동일. 온도사양은 Aviat -40~+85℃, Ceragon -30~+50℃로 등급 자체가 달라(산업용 vs 일반 옥외용 추정) 조건부로만 참고(확인 필요).</t>
         </is>
       </c>
     </row>
@@ -1244,15 +1258,20 @@
           <t>실내용 1G GbE SFP 광모듈</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>준직접 비교</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>74180</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="D3" s="4" t="n">
         <v>58309.385</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>양측 모두 실내형 1G Gigabit Ethernet SFP. 거리/파장 사양은 Aviat 자료에 명시되어 있지 않음(확인 필요).</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>양측 모두 실내형 1G Gigabit Ethernet SFP로 설명이 실질적으로 같아 3건 중 가장 근접한 매칭이다. 다만 거리/파장 사양이 Aviat 자료에 명시되어 있지 않아 완전 일치 확인은 아니다(확인 필요).</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1281,25 @@
           <t>10G SFP+ 광모듈(참고용, 완전 동일 사양 아님)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>참고 비교</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>67104.84600000001</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Aviat 품목은 산업용/실외 등급(-40~+85℃)이나 Ceragon 품목은 실외 등급 명시가 없어 완전히 동일한 사양은 아님 - 참고용 비교(확인 필요).</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Aviat 품목은 산업용/실외 등급(-40~+85℃)이나 Ceragon 품목은 실외 등급 명시가 없고 장거리(LR, 20km) 사양 - Aviat가 실제로 장거리 사양을 요구하는지도 불명확해 등급·거리 모두 완전히 동일한 사양은 아님 - 참고 수준 비교(확인 필요).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:E4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/13_대성단가_검토요약.xlsx
+++ b/output/13_대성단가_검토요약.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접대응_품목" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요약_판단'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요약_판단'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성별_비교상세'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'6+0_8+0_근거없음'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'직접대응_품목'!$A$1:$E$4</definedName>
@@ -485,10 +485,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -531,53 +531,65 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>직접대응 3건 결과</t>
+          <t>가장 중요한 한 문장(2026-09-08, 3차 검토에서 합의)</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SFP류 3건 모두 대성(Ceragon) 단가가 Aviat 판매가보다 낮게 나타나지만 신뢰도는 다르다: 실내용 1G SFP(준직접 비교, 설명 실질적 동일)가 가장 근접하고, 옥외용 1G SFP(조건부 비교, 온도등급 -40~+85℃ vs -30~+50℃로 다름)와 10G SFP+(참고 비교, 등급·거리 사양 모두 불일치 가능)는 그보다 약하다. 정식 견적 비교가 아니라 가격표상 단가 비교라는 한계도 여전하다(상세는 직접대응_품목 시트).</t>
+          <t>Aviat 11GHz 2+0 유력후보 19,088,472원(링크 환산 가정, 내부 참고값 - '사실상 확정'은 아님)은 대성보다 '싸다'는 뜻이 아니라, Aviat 쪽이 아직 완성 BoM 금액이 아니라는 뜻이다 - 14번 파일 기준 이 유력후보는 11개 핵심 기능군 중 5개(본체/무선송수신부/팬/라이선스/마운트)만 채우고, 대역결합기·인터페이스카드·제어카드·전원·SFP는 빠져 있다. 그래서 지금 단계의 실무적 결론은 '대성 가격이 비싸다/싸다'가 아니라 '아직 판단할 근거가 부족하다'이며, 대성 제시가를 반박할 근거도 확정할 근거도 없다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>구성 총액 검토(6+0/8+0)</t>
+          <t>직접대응 3건 결과</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>대성은 6+0/8+0도 완성 BoM·단가를 제시했으나, Aviat 발주이력에는 6+0/8+0(IAP3 계열)을 시사하는 근거가 전혀 없다 - 비교 대상 자체가 없으므로 이 두 구성은 대성 제시가를 검증할 방법이 현재 없다(애니콤 회신 또는 별도 시장가 조사 필요).</t>
+          <t>SFP류 3건 모두 대성(Ceragon) 단가가 Aviat 판매가보다 낮게 나타나지만 신뢰도는 다르다: 실내용 1G SFP(준직접 비교, 설명 실질적 동일)가 가장 근접하고, 옥외용 1G SFP(조건부 비교, 온도등급 -40~+85℃ vs -30~+50℃로 다름)와 10G SFP+(참고 비교, 등급·거리 사양 모두 불일치 가능)는 그보다 약하다. 정식 견적 비교가 아니라 가격표상 단가 비교라는 한계도 여전하다(상세는 직접대응_품목 시트).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>구성 총액 검토(2+0/4+0)</t>
+          <t>구성 총액 검토(6+0/8+0)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>11GHz 2+0은 Aviat 쪽에 그나마 가장 근거가 있다(독립 2개 이벤트로 확인된 핵심 품목 6종). 8GHz 2+0/4+0, 11GHz 4+0은 단일 이벤트 근거뿐이라 더 약하다. '구성별_비교상세' 시트에 품목수·범위 차이를 병기했으니, 대성 제시 품목 목록에 케이블/커넥터/전원 등이 빠짐없이 들어있는지 체크리스트로 대조하는 용도로 활용을 권한다(가격 수준 비교가 아니라 품목 누락 점검).</t>
+          <t>대성은 6+0/8+0도 완성 BoM·단가를 제시했으나, Aviat 발주이력에는 6+0/8+0(IAP3 계열)을 시사하는 근거가 전혀 없다 - 비교 대상 자체가 없으므로 이 두 구성은 대성 제시가를 검증할 방법이 현재 없다(애니콤 회신 또는 별도 시장가 조사 필요).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>구성 총액 검토(2+0/4+0)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>11GHz 2+0은 Aviat 쪽에 그나마 가장 근거가 있다(독립 2개 이벤트로 확인된 핵심 품목 6종). 8GHz 2+0/4+0, 11GHz 4+0은 단일 이벤트 근거뿐이라 더 약하다. '구성별_비교상세' 시트에 품목수·범위 차이를 병기했으니, 대성 제시 품목 목록에 케이블/커넥터/전원 등이 빠짐없이 들어있는지 체크리스트로 대조하는 용도로 활용을 권한다(가격 수준 비교가 아니라 품목 누락 점검).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>시한 내 권고</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>2026-09-16까지 애니콤 공식 회신이 오면 그 수치로 재검토. 회신이 늦어지면, 현재로선 대성 가격을 반박할 만한 동일 범위의 Aviat 총액이 없다는 점을 감안해 판단해야 한다(확정 반대 근거는 없음 = 확정 찬성 근거도 아님 - 별개의 문제).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/13_대성단가_검토요약.xlsx
+++ b/output/13_대성단가_검토요약.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직접대응_품목" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요약_판단'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요약_판단'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성별_비교상세'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'6+0_8+0_근거없음'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'직접대응_품목'!$A$1:$E$4</definedName>
@@ -105,6 +105,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -115,9 +118,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -588,8 +588,20 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>검토의견(안) - 2026-09-09 합의</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2+0/4+0(8GHz·11GHz): 대성인포텍이 제출한 Ceragon 제안가격에 대해 Aviat 측 표준 BoM 또는 동일 범위 가격자료가 확보되지 않아 직접적인 가격 우위·열위 판단은 불가능함. 다만 현재 확보된 자료 범위 내에서는 대성 제안가격이 현저히 과다하다는 객관적 근거 역시 확인되지 않음. 따라서 본 건은 가격 적정성이 입증되었다고 보기는 어려우나, 반대로 부적정하다고 판단할 근거도 부족하므로 현 시점에서는 조건부 수용 가능으로 판단함(요컨대 '싸다/비싸다'가 아니라 '가격 인하 요구의 근거가 부족하다'는 뜻). 6+0/8+0: Aviat 발주이력에 이 구성을 시사하는 근거 자체가 전혀 없어 위 2+0/4+0과는 근거 성격이 다르다 - '반박 근거 없음'이 아니라 '비교 대상 자체가 없음'이며, 별도의 시장가 조사 없이는 이 두 구성만 따로 조건부 수용 여부를 판단하기 어려움. 향후 애니콤 회신 또는 추가 시장자료 확보 시 전체 재검토를 권고함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -681,20 +693,20 @@
       <c r="C2" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>40476180</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>35608005.346</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n"/>
+      <c r="G2" s="5" t="n"/>
       <c r="H2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="6" t="n">
         <v>26915562</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -717,20 +729,20 @@
       <c r="C3" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>55941700</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>47710885.87799999</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="6" t="n">
         <v>26915562</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -753,20 +765,20 @@
       <c r="C4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>73770040</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>55704470.07800001</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="5" t="n"/>
       <c r="H4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <v>45820676</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -789,20 +801,20 @@
       <c r="C5" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>100727780</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>65924718.83999998</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n"/>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <v>45820676</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -825,22 +837,22 @@
       <c r="C6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>40476180</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>35608005.346</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>19088472</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>4364644</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -863,22 +875,22 @@
       <c r="C7" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>56118320</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>47709791.64199999</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>19088472</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>4364644</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -901,20 +913,20 @@
       <c r="C8" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>74123280</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>55702281.60600001</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="6" t="n">
         <v>35479732</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -937,20 +949,20 @@
       <c r="C9" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>101081020</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>65922530.36799998</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>35479732</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1022,10 +1034,10 @@
       <c r="C2" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>75626915.888</v>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1045,10 +1057,10 @@
       <c r="C3" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>83890988.12600002</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1068,10 +1080,10 @@
       <c r="C4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>91513678.52200001</v>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1091,10 +1103,10 @@
       <c r="C5" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>103910327.142</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1114,10 +1126,10 @@
       <c r="C6" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>75623633.18000001</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1137,10 +1149,10 @@
       <c r="C7" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>83887705.41800003</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1160,10 +1172,10 @@
       <c r="C8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>91509301.57800001</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1183,10 +1195,10 @@
       <c r="C9" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>103905950.198</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>없음 - 발주이력에 이 배수를 시사하는 근거 자체가 없음(공급사 확인 필요)</t>
         </is>
@@ -1252,10 +1264,10 @@
           <t>조건부 비교</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>130000</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>104257.351</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -1270,15 +1282,15 @@
           <t>실내용 1G GbE SFP 광모듈</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>준직접 비교</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>74180</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>58309.385</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1293,15 +1305,15 @@
           <t>10G SFP+ 광모듈(참고용, 완전 동일 사양 아님)</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>참고 비교</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>67104.84600000001</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
